--- a/15_Commodities/_template_COMMODITIES.xlsx
+++ b/15_Commodities/_template_COMMODITIES.xlsx
@@ -678,7 +678,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -748,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="9" t="str">
-        <f aca="false">IFERROR((C5/$C$5-1)*(365/D5),"-")</f>
+        <f aca="false">IFERROR((C5/$C$5-1)*(365/(D5-$D$5)),"-")</f>
         <v>-</v>
       </c>
       <c r="F5" s="9" t="str">
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="9" t="str">
-        <f aca="false">IFERROR((C6/$C$5-1)*(365/D6),"-")</f>
+        <f aca="false">IFERROR((C6/$C$5-1)*(365/(D6-$D$5)),"-")</f>
         <v>-</v>
       </c>
       <c r="F6" s="9" t="str">
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="9" t="str">
-        <f aca="false">IFERROR((C7/$C$5-1)*(365/D7),"-")</f>
+        <f aca="false">IFERROR((C7/$C$5-1)*(365/(D7-$D$5)),"-")</f>
         <v>-</v>
       </c>
       <c r="F7" s="9" t="str">
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="9" t="str">
-        <f aca="false">IFERROR((C8/$C$5-1)*(365/D8),"-")</f>
+        <f aca="false">IFERROR((C8/$C$5-1)*(365/(D8-$D$5)),"-")</f>
         <v>-</v>
       </c>
       <c r="F8" s="9" t="str">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="str">
-        <f aca="false">IFERROR((C9/$C$5-1)*(365/D9),"-")</f>
+        <f aca="false">IFERROR((C9/$C$5-1)*(365/(D9-$D$5)),"-")</f>
         <v>-</v>
       </c>
       <c r="F9" s="9" t="str">
@@ -914,7 +914,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
@@ -983,7 +983,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
@@ -1090,7 +1090,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G6"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
@@ -1189,7 +1189,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>

--- a/15_Commodities/_template_COMMODITIES.xlsx
+++ b/15_Commodities/_template_COMMODITIES.xlsx
@@ -3202,7 +3202,7 @@
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>IF(C9&lt;0,"REVIEW","PASS")</f>
+        <f>IF(ISNUMBER(C9),IF(C9&lt;0,"REVIEW","PASS"),"REVIEW")</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
